--- a/lessons-8-logic/Самопроверка_логика.xlsx
+++ b/lessons-8-logic/Самопроверка_логика.xlsx
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="O2" s="9">
-        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(D2&amp;""),"ё","е")=SUBSTITUTE(LOWER((B2&gt;=50)&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно")))</f>
+        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(D2&amp;""),"ё","е")=SUBSTITUTE(LOWER((B2&gt;=50)&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно")))</f>
         <v/>
       </c>
     </row>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="O3" s="9">
-        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B2&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B2&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -785,7 +785,7 @@
         </is>
       </c>
       <c r="O4" s="9">
-        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2)),NOT(_xlfn.ISFORMULA(C3)),NOT(_xlfn.ISFORMULA(C4)),NOT(_xlfn.ISFORMULA(C5)),NOT(_xlfn.ISFORMULA(C6)),NOT(_xlfn.ISFORMULA(C7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B2&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B3&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B4&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B5&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B6&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C7&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B7&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2)),NOT(_xlfn.ISFORMULA(C3)),NOT(_xlfn.ISFORMULA(C4)),NOT(_xlfn.ISFORMULA(C5)),NOT(_xlfn.ISFORMULA(C6)),NOT(_xlfn.ISFORMULA(C7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B2&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B3&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B4&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B5&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B6&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(C7&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B7&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="O5" s="9">
-        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6)),NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(E2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(E2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(E2-(IF(B2&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;=85,5,0))),FALSE),IFERROR(ABS(E3-(IF(B3&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;=85,5,0))),FALSE),IFERROR(ABS(E4-(IF(B4&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;=85,5,0))),FALSE),IFERROR(ABS(E5-(IF(B5&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;=85,5,0))),FALSE),IFERROR(ABS(E6-(IF(B6&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;=85,5,0))),FALSE),IFERROR(ABS(E7-(IF(B7&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B7&gt;=85,5,0))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6)),NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(E2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(E2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(E2-(IF(B2&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;=85,5,0))),FALSE),IFERROR(ABS(E3-(IF(B3&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;=85,5,0))),FALSE),IFERROR(ABS(E4-(IF(B4&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;=85,5,0))),FALSE),IFERROR(ABS(E5-(IF(B5&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;=85,5,0))),FALSE),IFERROR(ABS(E6-(IF(B6&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;=85,5,0))),FALSE),IFERROR(ABS(E7-(IF(B7&gt;=85,5,0)))&lt;=0.01*MAX(1,ABS(IF(B7&gt;=85,5,0))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="O6" s="9">
-        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6)),NOT(_xlfn.ISFORMULA(F7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(F2-(IF(C2="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C2="зачёт",1,0))),FALSE),IFERROR(ABS(F3-(IF(C3="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C3="зачёт",1,0))),FALSE),IFERROR(ABS(F4-(IF(C4="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C4="зачёт",1,0))),FALSE),IFERROR(ABS(F5-(IF(C5="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C5="зачёт",1,0))),FALSE),IFERROR(ABS(F6-(IF(C6="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C6="зачёт",1,0))),FALSE),IFERROR(ABS(F7-(IF(C7="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C7="зачёт",1,0))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6)),NOT(_xlfn.ISFORMULA(F7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(F2-(IF(C2="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C2="зачёт",1,0))),FALSE),IFERROR(ABS(F3-(IF(C3="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C3="зачёт",1,0))),FALSE),IFERROR(ABS(F4-(IF(C4="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C4="зачёт",1,0))),FALSE),IFERROR(ABS(F5-(IF(C5="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C5="зачёт",1,0))),FALSE),IFERROR(ABS(F6-(IF(C6="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C6="зачёт",1,0))),FALSE),IFERROR(ABS(F7-(IF(C7="зачёт",1,0)))&lt;=0.01*MAX(1,ABS(IF(C7="зачёт",1,0))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="O7" s="9">
-        <f>IF(ISBLANK(C3),"—",IF(NOT(AND(B3=50)),"✗ сначала измени B3 на 50",IF(OR(NOT(_xlfn.ISFORMULA(C3))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B3&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(C3),"—",IF(NOT(AND(B3=50)),"✗ сначала измени B3 на 50",IF(OR(NOT(_xlfn.ISFORMULA(C3))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(C3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(B3&gt;=50,"зачёт","незачёт"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
         </is>
       </c>
       <c r="O2" s="9">
-        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2)),NOT(_xlfn.ISFORMULA(C3)),NOT(_xlfn.ISFORMULA(C4)),NOT(_xlfn.ISFORMULA(C5)),NOT(_xlfn.ISFORMULA(C6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(C2-(IF(B2&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;=5000,0,700))),FALSE),IFERROR(ABS(C3-(IF(B3&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;=5000,0,700))),FALSE),IFERROR(ABS(C4-(IF(B4&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;=5000,0,700))),FALSE),IFERROR(ABS(C5-(IF(B5&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;=5000,0,700))),FALSE),IFERROR(ABS(C6-(IF(B6&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;=5000,0,700))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(C2),"—",IF(OR(NOT(_xlfn.ISFORMULA(C2)),NOT(_xlfn.ISFORMULA(C3)),NOT(_xlfn.ISFORMULA(C4)),NOT(_xlfn.ISFORMULA(C5)),NOT(_xlfn.ISFORMULA(C6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(C2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(C2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(C2-(IF(B2&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;=5000,0,700))),FALSE),IFERROR(ABS(C3-(IF(B3&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;=5000,0,700))),FALSE),IFERROR(ABS(C4-(IF(B4&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;=5000,0,700))),FALSE),IFERROR(ABS(C5-(IF(B5&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;=5000,0,700))),FALSE),IFERROR(ABS(C6-(IF(B6&gt;=5000,0,700)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;=5000,0,700))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
         </is>
       </c>
       <c r="O3" s="9">
-        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2)),NOT(_xlfn.ISFORMULA(D3)),NOT(_xlfn.ISFORMULA(D4)),NOT(_xlfn.ISFORMULA(D5)),NOT(_xlfn.ISFORMULA(D6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(D2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(D2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(D2-(IF(B2&gt;10000,B2*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;10000,B2*0.1,0))),FALSE),IFERROR(ABS(D3-(IF(B3&gt;10000,B3*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;10000,B3*0.1,0))),FALSE),IFERROR(ABS(D4-(IF(B4&gt;10000,B4*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;10000,B4*0.1,0))),FALSE),IFERROR(ABS(D5-(IF(B5&gt;10000,B5*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;10000,B5*0.1,0))),FALSE),IFERROR(ABS(D6-(IF(B6&gt;10000,B6*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;10000,B6*0.1,0))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2)),NOT(_xlfn.ISFORMULA(D3)),NOT(_xlfn.ISFORMULA(D4)),NOT(_xlfn.ISFORMULA(D5)),NOT(_xlfn.ISFORMULA(D6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(D2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(D2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(D2-(IF(B2&gt;10000,B2*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B2&gt;10000,B2*0.1,0))),FALSE),IFERROR(ABS(D3-(IF(B3&gt;10000,B3*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B3&gt;10000,B3*0.1,0))),FALSE),IFERROR(ABS(D4-(IF(B4&gt;10000,B4*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B4&gt;10000,B4*0.1,0))),FALSE),IFERROR(ABS(D5-(IF(B5&gt;10000,B5*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B5&gt;10000,B5*0.1,0))),FALSE),IFERROR(ABS(D6-(IF(B6&gt;10000,B6*0.1,0)))&lt;=0.01*MAX(1,ABS(IF(B6&gt;10000,B6*0.1,0))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1270,7 +1270,7 @@
         </is>
       </c>
       <c r="O4" s="9">
-        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(AND(IFERROR(ABS(E2-(B2+C2-D2))&lt;=0.01*MAX(1,ABS(B2+C2-D2)),FALSE),IFERROR(ABS(E3-(B3+C3-D3))&lt;=0.01*MAX(1,ABS(B3+C3-D3)),FALSE),IFERROR(ABS(E4-(B4+C4-D4))&lt;=0.01*MAX(1,ABS(B4+C4-D4)),FALSE),IFERROR(ABS(E5-(B5+C5-D5))&lt;=0.01*MAX(1,ABS(B5+C5-D5)),FALSE),IFERROR(ABS(E6-(B6+C6-D6))&lt;=0.01*MAX(1,ABS(B6+C6-D6)),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно")))</f>
+        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(AND(IFERROR(ABS(E2-(B2+C2-D2))&lt;=0.01*MAX(1,ABS(B2+C2-D2)),FALSE),IFERROR(ABS(E3-(B3+C3-D3))&lt;=0.01*MAX(1,ABS(B3+C3-D3)),FALSE),IFERROR(ABS(E4-(B4+C4-D4))&lt;=0.01*MAX(1,ABS(B4+C4-D4)),FALSE),IFERROR(ABS(E5-(B5+C5-D5))&lt;=0.01*MAX(1,ABS(B5+C5-D5)),FALSE),IFERROR(ABS(E6-(B6+C6-D6))&lt;=0.01*MAX(1,ABS(B6+C6-D6)),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно")))</f>
         <v/>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
         </is>
       </c>
       <c r="O5" s="9">
-        <f>IF(ISBLANK(E7),"—",IF(OR(NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(E7),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(E7),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(E7-(SUM(E2:E6)))&lt;=0.01*MAX(1,ABS(SUM(E2:E6))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E7),"—",IF(OR(NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(E7),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(E7),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(E7-(SUM(E2:E6)))&lt;=0.01*MAX(1,ABS(SUM(E2:E6))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         </is>
       </c>
       <c r="O6" s="9">
-        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E2&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E3&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E4&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E5&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E6&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E2&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E3&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E4&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E5&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(E6&gt;5000,"крупный","обычный"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1385,7 +1385,7 @@
         </is>
       </c>
       <c r="O7" s="9">
-        <f>IF(ISBLANK(E5),"—",IF(NOT(AND(B5=4900)),"✗ сначала измени B5 на 4900",IF(OR(NOT(_xlfn.ISFORMULA(E5))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(ABS(E5-(B5+C5-D5))&lt;=0.01*MAX(1,ABS(B5+C5-D5)),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E5),"—",IF(NOT(AND(B5=4900)),"✗ сначала измени B5 на 4900",IF(OR(NOT(_xlfn.ISFORMULA(E5))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(ABS(E5-(B5+C5-D5))&lt;=0.01*MAX(1,ABS(B5+C5-D5)),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1691,7 +1691,7 @@
         </is>
       </c>
       <c r="O2" s="9">
-        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(E2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&lt;=10,C2&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&lt;=10,C3&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&lt;=10,C4&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&lt;=10,C5&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&lt;=10,C6&gt;=150))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(E2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&lt;=10,C2&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&lt;=10,C3&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&lt;=10,C4&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&lt;=10,C5&gt;=150))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&lt;=10,C6&gt;=150))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="O3" s="9">
-        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(F2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&lt;=10,C2&gt;=150,D2&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&lt;=10,C3&gt;=150,D3&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&lt;=10,C4&gt;=150,D4&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&lt;=10,C5&gt;=150,D5&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&lt;=10,C6&gt;=150,D6&gt;=15))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(F2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&lt;=10,C2&gt;=150,D2&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&lt;=10,C3&gt;=150,D3&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&lt;=10,C4&gt;=150,D4&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&lt;=10,C5&gt;=150,D5&gt;=15))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&lt;=10,C6&gt;=150,D6&gt;=15))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="O4" s="9">
-        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(G2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(G2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(G2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(G2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(G2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B2&lt;=10,C2&gt;=150,D2&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B3&lt;=10,C3&gt;=150,D3&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B4&lt;=10,C4&gt;=150,D4&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B5&lt;=10,C5&gt;=150,D5&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B6&lt;=10,C6&gt;=150,D6&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно")))))</f>
+        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(G2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(G2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(G2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(G2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(G2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B2&lt;=10,C2&gt;=150,D2&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B3&lt;=10,C3&gt;=150,D3&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B4&lt;=10,C4&gt;=150,D4&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B5&lt;=10,C5&gt;=150,D5&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B6&lt;=10,C6&gt;=150,D6&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно")))))</f>
         <v/>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
         </is>
       </c>
       <c r="O5" s="9">
-        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(H2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(H2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(H2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(H2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(H2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C2&gt;=150,C2&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C3&gt;=150,C3&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C4&gt;=150,C4&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C5&gt;=150,C5&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C6&gt;=150,C6&lt;=180))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(H2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(H2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(H2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(H2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(H2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C2&gt;=150,C2&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C3&gt;=150,C3&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C4&gt;=150,C4&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C5&gt;=150,C5&lt;=180))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(C6&gt;=150,C6&lt;=180))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="O6" s="9">
-        <f>IF(ISBLANK(I2),"—",IF(OR(NOT(_xlfn.ISFORMULA(I2)),NOT(_xlfn.ISFORMULA(I3)),NOT(_xlfn.ISFORMULA(I4)),NOT(_xlfn.ISFORMULA(I5)),NOT(_xlfn.ISFORMULA(I6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(I2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(I2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(I2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F6))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(I2),"—",IF(OR(NOT(_xlfn.ISFORMULA(I2)),NOT(_xlfn.ISFORMULA(I3)),NOT(_xlfn.ISFORMULA(I4)),NOT(_xlfn.ISFORMULA(I5)),NOT(_xlfn.ISFORMULA(I6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(I2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(I2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(I2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(I6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(F6))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
         </is>
       </c>
       <c r="O7" s="9">
-        <f>IF(ISBLANK(G2),"—",IF(NOT(AND(D2=15)),"✗ сначала измени D2 на 15",IF(OR(NOT(_xlfn.ISFORMULA(G2))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B2&lt;=10,C2&gt;=150,D2&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(G2),"—",IF(NOT(AND(D2=15)),"✗ сначала измени D2 на 15",IF(OR(NOT(_xlfn.ISFORMULA(G2))),"✗ нужна формула, а не готовый ответ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(B2&lt;=10,C2&gt;=150,D2&gt;=15),"зачёт","пересдача"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="O2" s="9">
-        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2)),NOT(_xlfn.ISFORMULA(D3)),NOT(_xlfn.ISFORMULA(D4)),NOT(_xlfn.ISFORMULA(D5)),NOT(_xlfn.ISFORMULA(D6)),NOT(_xlfn.ISFORMULA(D7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(D2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(D2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(D2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B2&lt;7,B2&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B3&lt;7,B3&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B4&lt;7,B4&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B5&lt;7,B5&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B6&lt;7,B6&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D7&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B7&lt;7,B7&gt;65))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(D2),"—",IF(OR(NOT(_xlfn.ISFORMULA(D2)),NOT(_xlfn.ISFORMULA(D3)),NOT(_xlfn.ISFORMULA(D4)),NOT(_xlfn.ISFORMULA(D5)),NOT(_xlfn.ISFORMULA(D6)),NOT(_xlfn.ISFORMULA(D7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(D2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(D2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(D2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B2&lt;7,B2&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B3&lt;7,B3&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B4&lt;7,B4&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B5&lt;7,B5&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B6&lt;7,B6&gt;65))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(D7&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B7&lt;7,B7&gt;65))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="O3" s="9">
-        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6)),NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(E2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(E2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C2="сб",C2="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C3="сб",C3="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C4="сб",C4="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C5="сб",C5="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C6="сб",C6="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E7&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C7="сб",C7="вс"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6)),NOT(_xlfn.ISFORMULA(E7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(E2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(E2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C2="сб",C2="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C3="сб",C3="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C4="сб",C4="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C5="сб",C5="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C6="сб",C6="вс"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E7&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(C7="сб",C7="вс"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="O4" s="9">
-        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6)),NOT(_xlfn.ISFORMULA(F7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(F2-(IF(E2,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E2,2500,1800))),FALSE),IFERROR(ABS(F3-(IF(E3,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E3,2500,1800))),FALSE),IFERROR(ABS(F4-(IF(E4,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E4,2500,1800))),FALSE),IFERROR(ABS(F5-(IF(E5,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E5,2500,1800))),FALSE),IFERROR(ABS(F6-(IF(E6,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E6,2500,1800))),FALSE),IFERROR(ABS(F7-(IF(E7,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E7,2500,1800))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6)),NOT(_xlfn.ISFORMULA(F7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(F2-(IF(E2,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E2,2500,1800))),FALSE),IFERROR(ABS(F3-(IF(E3,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E3,2500,1800))),FALSE),IFERROR(ABS(F4-(IF(E4,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E4,2500,1800))),FALSE),IFERROR(ABS(F5-(IF(E5,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E5,2500,1800))),FALSE),IFERROR(ABS(F6-(IF(E6,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E6,2500,1800))),FALSE),IFERROR(ABS(F7-(IF(E7,2500,1800)))&lt;=0.01*MAX(1,ABS(IF(E7,2500,1800))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         </is>
       </c>
       <c r="O5" s="9">
-        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6)),NOT(_xlfn.ISFORMULA(G7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(G2-(IF(D2,F2/2,F2)))&lt;=0.01*MAX(1,ABS(IF(D2,F2/2,F2))),FALSE),IFERROR(ABS(G3-(IF(D3,F3/2,F3)))&lt;=0.01*MAX(1,ABS(IF(D3,F3/2,F3))),FALSE),IFERROR(ABS(G4-(IF(D4,F4/2,F4)))&lt;=0.01*MAX(1,ABS(IF(D4,F4/2,F4))),FALSE),IFERROR(ABS(G5-(IF(D5,F5/2,F5)))&lt;=0.01*MAX(1,ABS(IF(D5,F5/2,F5))),FALSE),IFERROR(ABS(G6-(IF(D6,F6/2,F6)))&lt;=0.01*MAX(1,ABS(IF(D6,F6/2,F6))),FALSE),IFERROR(ABS(G7-(IF(D7,F7/2,F7)))&lt;=0.01*MAX(1,ABS(IF(D7,F7/2,F7))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6)),NOT(_xlfn.ISFORMULA(G7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(G2-(IF(D2,F2/2,F2)))&lt;=0.01*MAX(1,ABS(IF(D2,F2/2,F2))),FALSE),IFERROR(ABS(G3-(IF(D3,F3/2,F3)))&lt;=0.01*MAX(1,ABS(IF(D3,F3/2,F3))),FALSE),IFERROR(ABS(G4-(IF(D4,F4/2,F4)))&lt;=0.01*MAX(1,ABS(IF(D4,F4/2,F4))),FALSE),IFERROR(ABS(G5-(IF(D5,F5/2,F5)))&lt;=0.01*MAX(1,ABS(IF(D5,F5/2,F5))),FALSE),IFERROR(ABS(G6-(IF(D6,F6/2,F6)))&lt;=0.01*MAX(1,ABS(IF(D6,F6/2,F6))),FALSE),IFERROR(ABS(G7-(IF(D7,F7/2,F7)))&lt;=0.01*MAX(1,ABS(IF(D7,F7/2,F7))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
         </is>
       </c>
       <c r="O6" s="9">
-        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6)),NOT(_xlfn.ISFORMULA(H7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(H2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(H2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E6))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H7&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E7))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6)),NOT(_xlfn.ISFORMULA(H7))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(H2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(H2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E6))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H7&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E7))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2413,7 +2413,7 @@
         </is>
       </c>
       <c r="O7" s="9">
-        <f>IF(ISBLANK(G8),"—",IF(OR(NOT(_xlfn.ISFORMULA(G8))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(G8),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(G8),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(G8-(SUM(G2:G7)))&lt;=0.01*MAX(1,ABS(SUM(G2:G7))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(G8),"—",IF(OR(NOT(_xlfn.ISFORMULA(G8))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(G8),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(G8),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(G8-(SUM(G2:G7)))&lt;=0.01*MAX(1,ABS(SUM(G2:G7))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="O2" s="9">
-        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(E2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&gt;=4.5,C2&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&gt;=4.5,C3&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&gt;=4.5,C4&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&gt;=4.5,C5&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&gt;=4.5,C6&lt;=5))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(E2),"—",IF(OR(NOT(_xlfn.ISFORMULA(E2)),NOT(_xlfn.ISFORMULA(E3)),NOT(_xlfn.ISFORMULA(E4)),NOT(_xlfn.ISFORMULA(E5)),NOT(_xlfn.ISFORMULA(E6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(E2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(E2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(E2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(E2&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B2&gt;=4.5,C2&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E3&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B3&gt;=4.5,C3&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E4&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B4&gt;=4.5,C4&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E5&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B5&gt;=4.5,C5&lt;=5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(E6&amp;""),"ё","е")=SUBSTITUTE(LOWER((AND(B6&gt;=4.5,C6&lt;=5))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +2770,7 @@
         </is>
       </c>
       <c r="O3" s="9">
-        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(F2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E2,D2="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E3,D3="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E4,D4="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E5,D5="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E6,D6="да"),"да","нет"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно")))))</f>
+        <f>IF(ISBLANK(F2),"—",IF(OR(NOT(_xlfn.ISFORMULA(F2)),NOT(_xlfn.ISFORMULA(F3)),NOT(_xlfn.ISFORMULA(F4)),NOT(_xlfn.ISFORMULA(F5)),NOT(_xlfn.ISFORMULA(F6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(F2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(F2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(OR(ISNUMBER(SEARCH("AND(",IFERROR(_xlfn.FORMULATEXT(F2),""))),(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"И(","")))/2&gt;(LEN(IFERROR(_xlfn.FORMULATEXT(F2),""))-LEN(SUBSTITUTE(UPPER(IFERROR(_xlfn.FORMULATEXT(F2),"")),"ЛИ(","")))/3)),"✗ нужна функция И",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(F2&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E2,D2="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F3&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E3,D3="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F4&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E4,D4="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F5&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E5,D5="да"),"да","нет"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(F6&amp;""),"ё","е")=SUBSTITUTE(LOWER((IF(AND(E6,D6="да"),"да","нет"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно")))))</f>
         <v/>
       </c>
     </row>
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="O4" s="9">
-        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B2=5,D2="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B3=5,D3="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B4=5,D4="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B5=5,D5="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B6=5,D6="да"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(G2),"—",IF(OR(NOT(_xlfn.ISFORMULA(G2)),NOT(_xlfn.ISFORMULA(G3)),NOT(_xlfn.ISFORMULA(G4)),NOT(_xlfn.ISFORMULA(G5)),NOT(_xlfn.ISFORMULA(G6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ИЛИ(",IFERROR(_xlfn.FORMULATEXT(G2),""))),ISNUMBER(SEARCH("OR(",IFERROR(_xlfn.FORMULATEXT(G2),""))))),"✗ нужна функция ИЛИ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(G2&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B2=5,D2="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G3&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B3=5,D3="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G4&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B4=5,D4="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G5&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B5=5,D5="да"))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(G6&amp;""),"ё","е")=SUBSTITUTE(LOWER((OR(B6=5,D6="да"))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
         </is>
       </c>
       <c r="O5" s="9">
-        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(H2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(H2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E6))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(H2),"—",IF(OR(NOT(_xlfn.ISFORMULA(H2)),NOT(_xlfn.ISFORMULA(H3)),NOT(_xlfn.ISFORMULA(H4)),NOT(_xlfn.ISFORMULA(H5)),NOT(_xlfn.ISFORMULA(H6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("НЕ(",IFERROR(_xlfn.FORMULATEXT(H2),""))),ISNUMBER(SEARCH("NOT(",IFERROR(_xlfn.FORMULATEXT(H2),""))))),"✗ нужна функция НЕ",IF(NOT(AND(IFERROR(SUBSTITUTE(LOWER(H2&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E2))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H3&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E3))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H4&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E4))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H5&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E5))&amp;""),"ё","е"),FALSE),IFERROR(SUBSTITUTE(LOWER(H6&amp;""),"ё","е")=SUBSTITUTE(LOWER((NOT(E6))&amp;""),"ё","е"),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="O6" s="9">
-        <f>IF(ISBLANK(I2),"—",IF(OR(NOT(_xlfn.ISFORMULA(I2)),NOT(_xlfn.ISFORMULA(I3)),NOT(_xlfn.ISFORMULA(I4)),NOT(_xlfn.ISFORMULA(I5)),NOT(_xlfn.ISFORMULA(I6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(I2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(I2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(I2-(IF(F2="да",60000,IF(E2,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F2="да",60000,IF(E2,40000,0)))),FALSE),IFERROR(ABS(I3-(IF(F3="да",60000,IF(E3,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F3="да",60000,IF(E3,40000,0)))),FALSE),IFERROR(ABS(I4-(IF(F4="да",60000,IF(E4,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F4="да",60000,IF(E4,40000,0)))),FALSE),IFERROR(ABS(I5-(IF(F5="да",60000,IF(E5,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F5="да",60000,IF(E5,40000,0)))),FALSE),IFERROR(ABS(I6-(IF(F6="да",60000,IF(E6,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F6="да",60000,IF(E6,40000,0)))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(I2),"—",IF(OR(NOT(_xlfn.ISFORMULA(I2)),NOT(_xlfn.ISFORMULA(I3)),NOT(_xlfn.ISFORMULA(I4)),NOT(_xlfn.ISFORMULA(I5)),NOT(_xlfn.ISFORMULA(I6))),"✗ нужна формула, а не готовый ответ (протяни формулу вниз)",IF(NOT(OR(ISNUMBER(SEARCH("ЕСЛИ(",IFERROR(_xlfn.FORMULATEXT(I2),""))),ISNUMBER(SEARCH("IF(",IFERROR(_xlfn.FORMULATEXT(I2),""))))),"✗ нужна функция ЕСЛИ",IF(NOT(AND(IFERROR(ABS(I2-(IF(F2="да",60000,IF(E2,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F2="да",60000,IF(E2,40000,0)))),FALSE),IFERROR(ABS(I3-(IF(F3="да",60000,IF(E3,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F3="да",60000,IF(E3,40000,0)))),FALSE),IFERROR(ABS(I4-(IF(F4="да",60000,IF(E4,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F4="да",60000,IF(E4,40000,0)))),FALSE),IFERROR(ABS(I5-(IF(F5="да",60000,IF(E5,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F5="да",60000,IF(E5,40000,0)))),FALSE),IFERROR(ABS(I6-(IF(F6="да",60000,IF(E6,40000,0))))&lt;=0.01*MAX(1,ABS(IF(F6="да",60000,IF(E6,40000,0)))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
@@ -2938,7 +2938,7 @@
         </is>
       </c>
       <c r="O7" s="9">
-        <f>IF(ISBLANK(I8),"—",IF(OR(NOT(_xlfn.ISFORMULA(I8))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(I8),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(I8),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(I8-(SUM(I2:I6)))&lt;=0.01*MAX(1,ABS(SUM(I2:I6))),FALSE))),"✗ ответ неверный — проверь условие, знак на границе и кавычки","✓ верно"))))</f>
+        <f>IF(ISBLANK(I8),"—",IF(OR(NOT(_xlfn.ISFORMULA(I8))),"✗ нужна формула, а не готовый ответ",IF(NOT(OR(ISNUMBER(SEARCH("СУММ(",IFERROR(_xlfn.FORMULATEXT(I8),""))),ISNUMBER(SEARCH("SUM(",IFERROR(_xlfn.FORMULATEXT(I8),""))))),"✗ нужна функция СУММ",IF(NOT(AND(IFERROR(ABS(I8-(SUM(I2:I6)))&lt;=0.01*MAX(1,ABS(SUM(I2:I6))),FALSE))),"✗ ответ неверный — проверь формулу и диапазон","✓ верно"))))</f>
         <v/>
       </c>
     </row>
